--- a/forms/trg/Formulir_TRG_straac.xlsx
+++ b/forms/trg/Formulir_TRG_straac.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B22)</f>
+        <f>COUNTA(Anggota!B5:B23)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F22)</f>
+        <f>COUNTA(Anggota!F5:F23)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,18 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr, Ratna Ayu Damayanti, Ak.,MSoc.Sc.,CA</t>
+          <t>Prof. Dr. Syarifuddin, Ak., MSoc.Sc.,CA</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Faculty of Economics and Business, Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Local Government Finance, Public Sector Accounting, Environmental Accounting</t>
+          <t>Public Sector Accounting, Political Budgeting, Auditing</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -937,17 +933,17 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-2867-6315</t>
+          <t>0000-0002-7880-9331</t>
         </is>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>6026234</t>
+          <t>6026231</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57191409590</t>
+          <t>57219211497</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -962,12 +958,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Afdal Madein, PhD, CA</t>
+          <t>Dr, Ratna Ayu Damayanti, Ak.,MSoc.Sc.,CA</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -977,7 +973,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Management Accounting, Sustainability Accounting, Social Accounting, Environmental Accounting</t>
+          <t>Local Government Finance, Public Sector Accounting, Environmental Accounting</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -986,17 +982,17 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-2623-8204</t>
+          <t>0000-0002-2867-6315</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>6057177</t>
+          <t>6026234</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>56884825100</t>
+          <t>57191409590</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -1011,22 +1007,22 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Kashan Pirzada</t>
+          <t>Afdal Madein, PhD, CA</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Birmingham City University</t>
+          <t>Faculty of Economics and Business, Hasanuddin University</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Corporate Governance, Accountability, Corporate Reporting, Corporate Disclosure, CSR/Sustainability</t>
+          <t>Management Accounting, Sustainability Accounting, Social Accounting, Environmental Accounting</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1035,13 +1031,17 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-1186-0631</t>
-        </is>
-      </c>
-      <c r="K7" s="12" t="n"/>
+          <t>0000-0003-2623-8204</t>
+        </is>
+      </c>
+      <c r="K7" s="11" t="inlineStr">
+        <is>
+          <t>6057177</t>
+        </is>
+      </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>57191988829</t>
+          <t>56884825100</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1056,22 +1056,22 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Khalid Eltayeb Elfaki Adam</t>
+          <t>Dr. Kashan Pirzada</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Faculty of Business and Management, UCSI university, Kuala Lumpur, Malaysia</t>
+          <t>Birmingham City University</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Development economics, Environmental sustainability, and macroeconomics</t>
+          <t>Corporate Governance, Accountability, Corporate Reporting, Corporate Disclosure, CSR/Sustainability</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1080,13 +1080,13 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-8728-0492</t>
+          <t>0000-0003-1186-0631</t>
         </is>
       </c>
       <c r="K8" s="12" t="n"/>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>57203807123</t>
+          <t>57191988829</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1101,33 +1101,37 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Wahyuni</t>
+          <t>Khalid Eltayeb Elfaki Adam</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Universitas Hasanuddin</t>
+          <t>Faculty of Business and Management, UCSI university, Kuala Lumpur, Malaysia</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Sustainability Accounting</t>
+          <t>Development economics, Environmental sustainability, and macroeconomics</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-8728-0492</t>
+        </is>
+      </c>
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>60543564300</t>
+          <t>57203807123</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1142,12 +1146,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Gafur Kadar</t>
+          <t>Wahyuni</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1157,24 +1161,20 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Finance, and Sustainability Accounting</t>
+          <t>Sustainability Accounting</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>0009-0008-9088-7763</t>
-        </is>
-      </c>
-      <c r="K10" s="11" t="inlineStr">
-        <is>
-          <t>6674673</t>
-        </is>
-      </c>
-      <c r="L10" s="12" t="n"/>
+      <c r="J10" s="12" t="n"/>
+      <c r="K10" s="12" t="n"/>
+      <c r="L10" s="11" t="inlineStr">
+        <is>
+          <t>60543564300</t>
+        </is>
+      </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1185,18 +1185,46 @@
       <c r="A11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="11" t="n"/>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Muhammad Gafur Kadar</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Universitas Hasanuddin</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Finance, and Sustainability Accounting</t>
+        </is>
+      </c>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
-      <c r="J11" s="12" t="n"/>
-      <c r="K11" s="12" t="n"/>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>0009-0008-9088-7763</t>
+        </is>
+      </c>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>6674673</t>
+        </is>
+      </c>
       <c r="L11" s="12" t="n"/>
-      <c r="M11" s="12" t="n"/>
+      <c r="M11" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -1385,15 +1413,32 @@
       <c r="L22" s="12" t="n"/>
       <c r="M22" s="12" t="n"/>
     </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="12" t="n"/>
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="11" t="n"/>
+      <c r="F23" s="12" t="n"/>
+      <c r="G23" s="12" t="n"/>
+      <c r="H23" s="12" t="n"/>
+      <c r="I23" s="12" t="n"/>
+      <c r="J23" s="12" t="n"/>
+      <c r="K23" s="12" t="n"/>
+      <c r="L23" s="12" t="n"/>
+      <c r="M23" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
